--- a/output/pdf_financials_xlsx/ISP.xlsx
+++ b/output/pdf_financials_xlsx/ISP.xlsx
@@ -2225,16 +2225,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.065501</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.244201</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.301501</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.537855</v>
       </c>
     </row>
     <row r="93">
@@ -3496,7 +3496,11 @@
           <t>SHARE-BASED PAYMENTS RESERVE (Note 6)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3830,7 +3834,11 @@
           <t>SHARE-BASED PAYMENTS RESERVE (Note 7)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -4016,7 +4024,11 @@
           <t>SHARE-BASED PAYMENTS RESERVE (Note 6)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>0.065501</v>
       </c>

--- a/output/pdf_financials_xlsx/ISP.xlsx
+++ b/output/pdf_financials_xlsx/ISP.xlsx
@@ -1079,16 +1079,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.21192</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.169293</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001996</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="35">
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.21192</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.169293</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001996</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="37">
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.21192</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.241026</v>
+        <v>0.07173300000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.032329</v>
+        <v>0.030333</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.259074</v>
+        <v>0.013274</v>
       </c>
     </row>
     <row r="49">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/ISP.xlsx
+++ b/output/pdf_financials_xlsx/ISP.xlsx
@@ -5874,7 +5874,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E77" s="5" t="n">
         <v>0.37</v>
       </c>
